--- a/data/trans_orig/IP74A2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP74A2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto el alquiler en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos del alquiler en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
